--- a/docs/tecnico/OnBoardPro-Backlog.xlsx
+++ b/docs/tecnico/OnBoardPro-Backlog.xlsx
@@ -6,19 +6,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Épicas" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definición de Hecho" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Habilitadores técnicos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riesgos" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documentación" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medallas" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Condiciones y disparadores" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escalas" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan de Sprints" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Métricas por sprint" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bugs" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan de Sprints" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Métricas por sprint" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bugs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alcance por modulo" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backlog'!$A$1:$O$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Medallas'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -131,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -155,6 +150,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -269,30 +265,6 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Métricas por sprint'!F1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Métricas por sprint'!$A$2:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Métricas por sprint'!$F$2:$F$7</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
               <f>'Métricas por sprint'!G1</f>
             </strRef>
           </tx>
@@ -309,6 +281,30 @@
           <val>
             <numRef>
               <f>'Métricas por sprint'!$G$2:$G$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Métricas por sprint'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Métricas por sprint'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Métricas por sprint'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -405,38 +401,6 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Métricas por sprint'!I1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Métricas por sprint'!$A$2:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Métricas por sprint'!$I$2:$I$7</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
               <f>'Métricas por sprint'!J1</f>
             </strRef>
           </tx>
@@ -461,6 +425,38 @@
           <val>
             <numRef>
               <f>'Métricas por sprint'!$J$2:$J$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Métricas por sprint'!K1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Métricas por sprint'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Métricas por sprint'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -557,7 +553,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Métricas por sprint'!K1</f>
+              <f>'Métricas por sprint'!L1</f>
             </strRef>
           </tx>
           <spPr>
@@ -572,7 +568,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Métricas por sprint'!$K$2:$K$7</f>
+              <f>'Métricas por sprint'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -646,7 +642,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>14</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -668,7 +664,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>14</col>
       <colOff>0</colOff>
       <row>19</row>
       <rowOff>0</rowOff>
@@ -690,7 +686,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>14</col>
       <colOff>0</colOff>
       <row>37</row>
       <rowOff>0</rowOff>
@@ -6446,7 +6442,581 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="82" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Épica</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>En MVP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" customFormat="1" s="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Plataforma y Multi-tenancy</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Que varias organizaciones convivan en la misma instalación sin verse entre sí. Es el cimiento comercial del producto.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" s="2">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Autenticación y Acceso</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Entrar al sistema de forma segura por credenciales propias o proveedores corporativos.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" s="2">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Usuarios y Roles</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Administrar las personas de cada organización y lo que cada una puede hacer.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" s="2">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Grupos</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Agrupar aprendices para asignarles cursos en bloque, en vez de uno por uno.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" s="2">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Cursos y Estructura de Contenido</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Organizar el contenido formativo en cursos con secciones ordenados.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" s="2">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Actividades y Recursos Multimedia</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Cargar y consumir el material de apoyo: videos, PDFs, enlaces.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" s="2">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Evaluaciones</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>El examen de siempre y el motor que presenta preguntas y las califica. Ese mismo motor es el que después reutilizan los juegos.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" s="2">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Entregas y Calificación</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Que el aprendiz entregue trabajos y el instructor los califique con retroalimentación.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" s="2">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Gamificación: XP y Niveles</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>La economía de puntos que sostiene toda la motivación del producto.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" s="2">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Gamificación: Logros</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Metas desbloqueables que premian conductas específicas.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" s="2">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>E11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Juegos Autogenerables</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>El instructor elige qué juego quiere, carga solo los datos que ese juego pide, y el sistema lo arma e inserta en la sección.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" s="2">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>E12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Perfil de Usuario</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Que cada persona gestione sus datos y vea su progreso.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" s="2">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>E13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Notificaciones</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Avisar de lo que requiere atención sin que el usuario tenga que entrar a buscarlo.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" s="2">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Reportes y Analítica</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Datos de avance y uso. Es lo que justifica la renovación del contrato ante un cliente.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Criterio (aplica a TODA historia)</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" customFormat="1" s="2">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>La historia se demuestra funcionando de punta a punta: interfaz y servicio, no uno solo de los dos.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Se cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" customFormat="1" s="2">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Las reglas de rol se cumplen y se probaron con al menos un usuario de cada rol implicado.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Se cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" customFormat="1" s="2">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Ningún dato de otra organización es accesible desde la historia entregada.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Se cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" customFormat="1" s="2">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Tiene pruebas automatizadas de camino feliz y de acceso denegado.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>No se cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" customFormat="1" s="2">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Los errores devuelven mensajes comprensibles, sin exponer detalles internos.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Se cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" customFormat="1" s="2">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Está documentada en la especificación de la API y en la colección de pruebas.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Se cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" customFormat="1" s="2">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Fue revisada por otra persona del equipo antes de integrarse.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Se cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" customFormat="1" s="2">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Se demostró en la revisión de sprint sobre el entorno desplegado, no en local.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Se cumple</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6465,807 +7035,1024 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Inicio</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Fin</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Historias</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Claves Jira</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="E2" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="F2" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>HU-007, HU-069, HU-009, HU-011, HU-008</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="E3" s="10" t="n">
+      <c r="E3" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="10" t="n">
+      <c r="F3" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>HU-001, HU-014, HU-002</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>HU-026, HU-006, HU-010, HU-013, HU-020, HU-071</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>HU-015, HU-032, HU-023, HU-027</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>HU-016, HU-022, HU-021, HU-017, HU-018</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>HU-034, HU-005, HU-003, HU-025, HU-036, HU-041, HU-046, HU-051, HU-004</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>En curso</t>
         </is>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>HU-070, HU-024, HU-037, HU-040, HU-048, HU-039, HU-058, HU-059</t>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>HU-059, HU-039, HU-058, HU-040, HU-037, HU-070, HU-024, HU-048</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Sprint 8</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Planificado</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>HU-028, HU-044, HU-052, HU-029, HU-033, HU-053</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Sprint 9</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>2026-11-07</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Planificado</t>
         </is>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>HU-030, HU-031, HU-045, HU-065, HU-055, HU-060</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Sprint 10</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>2026-11-14</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Planificado</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>HU-035, HU-038, HU-047, HU-054, HU-067, HU-061, HU-062</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Sprint 11</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Planificado</t>
         </is>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>HU-049, HU-056, HU-057, HU-019, HU-043</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr"/>
-      <c r="C13" s="10" t="inlineStr"/>
-      <c r="D13" s="10" t="inlineStr"/>
-      <c r="E13" s="10" t="n">
+      <c r="B13" s="11" t="inlineStr"/>
+      <c r="C13" s="11" t="inlineStr"/>
+      <c r="D13" s="11" t="inlineStr"/>
+      <c r="E13" s="11" t="n">
         <v>64</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="11" t="n">
         <v>226</v>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>MVP completo</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Backlog (post-MVP)</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr"/>
-      <c r="C14" s="10" t="inlineStr"/>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr"/>
+      <c r="C14" s="11" t="inlineStr"/>
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Sin planificar</t>
         </is>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="11" t="n">
         <v>66</v>
       </c>
-      <c r="G14" s="10" t="inlineStr"/>
+      <c r="G14" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Inicio</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Fin</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Historias comprometidas</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Historias completadas</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
-        <is>
-          <t>SP comprometidos</t>
-        </is>
-      </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>SP pronosticados</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>SP completados</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>% del pronóstico</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>SP acumulados</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Alcance total del MVP</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Bugs detectados</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="F2" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="G2" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="H2" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="H2" s="12" t="n">
+      <c r="I2" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="J2" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="J2" s="10" t="n">
+      <c r="K2" s="11" t="n">
         <v>226</v>
       </c>
-      <c r="K2" s="10" t="n">
+      <c r="L2" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n">
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E3" s="10" t="n">
+      <c r="F3" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="10" t="n">
+      <c r="G3" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="G3" s="10" t="n">
+      <c r="H3" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="H3" s="12" t="n">
+      <c r="I3" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="10" t="n">
+      <c r="J3" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="J3" s="10" t="n">
+      <c r="K3" s="11" t="n">
         <v>226</v>
       </c>
-      <c r="K3" s="10" t="n">
+      <c r="L3" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="F4" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="G4" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="H4" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="I4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="J4" s="11" t="n">
         <v>44</v>
       </c>
-      <c r="J4" s="10" t="n">
+      <c r="K4" s="11" t="n">
         <v>226</v>
       </c>
-      <c r="K4" s="10" t="n">
+      <c r="L4" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="F5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="G5" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="H5" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="I5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="J5" s="11" t="n">
         <v>61</v>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="K5" s="11" t="n">
         <v>226</v>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="L5" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="F6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="G6" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="H6" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.6842</v>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="J6" s="11" t="n">
         <v>74</v>
       </c>
-      <c r="J6" s="10" t="n">
+      <c r="K6" s="11" t="n">
         <v>226</v>
       </c>
-      <c r="K6" s="10" t="n">
+      <c r="L6" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="F7" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="G7" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="H7" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="I7" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="10" t="n">
+      <c r="J7" s="11" t="n">
         <v>103</v>
       </c>
-      <c r="J7" s="10" t="n">
+      <c r="K7" s="11" t="n">
         <v>226</v>
       </c>
-      <c r="K7" s="10" t="n">
+      <c r="L7" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr"/>
-      <c r="C8" s="10" t="inlineStr"/>
-      <c r="D8" s="10" t="n">
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="13" t="n"/>
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="11" t="n">
+        <v>226</v>
+      </c>
+      <c r="L8" s="11" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Sprint 8</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Planificado</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="11" t="n">
+        <v>226</v>
+      </c>
+      <c r="L9" s="11" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Sprint 9</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Planificado</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="13" t="n"/>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="11" t="n">
+        <v>226</v>
+      </c>
+      <c r="L10" s="11" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Sprint 10</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Planificado</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="13" t="n"/>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="11" t="n">
+        <v>226</v>
+      </c>
+      <c r="L11" s="11" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Sprint 11</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Planificado</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="13" t="n"/>
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="11" t="n">
+        <v>226</v>
+      </c>
+      <c r="L12" s="11" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Cerrados</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr"/>
+      <c r="C13" s="11" t="inlineStr"/>
+      <c r="D13" s="11" t="inlineStr"/>
+      <c r="E13" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="F13" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="G13" s="11" t="n">
         <v>109</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="H13" s="11" t="n">
         <v>103</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.945</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="J13" s="11" t="n">
         <v>103</v>
       </c>
-      <c r="J8" s="10" t="n">
+      <c r="K13" s="11" t="n">
         <v>226</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="L13" s="11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -7275,7 +8062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7292,327 +8079,327 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Defecto</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>B-01</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>Los errores de validacion se devolvian como 500 Required en lugar de 400 indicando el campo.</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Funcional</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>B-02</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Varios endpoints no filtraban por organizacion: se podian consultar datos de otra empresa.</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>B-03</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>Rutas de grupos sin verificacion de sesion.</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Un administrador podia cambiar el rol de un superadministrador y el de usuarios de otra organizacion.</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>B-05</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>CORS rechazaba localhost y bloqueaba el desarrollo del frontend.</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Configuracion</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>B-06</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>PayloadTooLargeError al subir archivos: el frontend los enviaba en base64 dentro de un JSON.</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Funcional</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>B-07</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>deliverable: Expected boolean, received string al crear actividades por multipart.</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Funcional</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>B-08</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>TanStack en una version con vulnerabilidad conocida.</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Dependencias</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Mitigado</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>B-09</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Un examen devolvia las respuestas correctas al aprendiz que lo iba a rendir.</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>B-10</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>El XP se acreditaba al subir la entrega y no al aprobarla, y volver a aprobar duplicaba los puntos.</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Funcional</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>B-11</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Actividades y examenes editables por un instructor que no dictaba ese curso.</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>B-12</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>El limite del cuerpo JSON cortaba las entregas con comentarios largos.</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Funcional</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
@@ -7620,1364 +8407,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="82" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Épica</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Objetivo</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>En MVP</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Plataforma y Multi-tenancy</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Que varias organizaciones convivan en la misma instalación sin verse entre sí. Es el cimiento comercial del producto.</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="2">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>E02</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Autenticación y Acceso</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Entrar al sistema de forma segura por credenciales propias o proveedores corporativos.</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" s="2">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Usuarios y Roles</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Administrar las personas de cada organización y lo que cada una puede hacer.</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" s="2">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Grupos</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Agrupar aprendices para asignarles cursos en bloque, en vez de uno por uno.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" s="2">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>E05</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Cursos y Estructura de Contenido</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Organizar el contenido formativo en cursos con secciones ordenados.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" s="2">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>E06</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Actividades y Recursos Multimedia</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Cargar y consumir el material de apoyo: videos, PDFs, enlaces.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" s="2">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>E07</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Evaluaciones</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>El examen de siempre y el motor que presenta preguntas y las califica. Ese mismo motor es el que después reutilizan los juegos.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" s="2">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>E08</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Entregas y Calificación</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Que el aprendiz entregue trabajos y el instructor los califique con retroalimentación.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" s="2">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>E09</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Gamificación: XP y Niveles</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>La economía de puntos que sostiene toda la motivación del producto.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" s="2">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>E10</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Gamificación: Logros</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Metas desbloqueables que premian conductas específicas.</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" s="2">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>E11</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Juegos Autogenerables</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>El instructor elige qué juego quiere, carga solo los datos que ese juego pide, y el sistema lo arma e inserta en la sección.</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" s="2">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Perfil de Usuario</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Que cada persona gestione sus datos y vea su progreso.</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" s="2">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>E13</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Notificaciones</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Avisar de lo que requiere atención sin que el usuario tenga que entrar a buscarlo.</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" s="2">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>E14</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Reportes y Analítica</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Datos de avance y uso. Es lo que justifica la renovación del contrato ante un cliente.</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Criterio (aplica a TODA historia)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="2">
-      <c r="A2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>La historia se demuestra funcionando de punta a punta: interfaz y servicio, no uno solo de los dos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="2">
-      <c r="A3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Las reglas de rol se cumplen y se probaron con al menos un usuario de cada rol implicado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" customFormat="1" s="2">
-      <c r="A4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Ningún dato de otra organización es accesible desde la historia entregada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" customFormat="1" s="2">
-      <c r="A5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Tiene pruebas automatizadas de camino feliz y de acceso denegado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" customFormat="1" s="2">
-      <c r="A6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Los errores devuelven mensajes comprensibles, sin exponer detalles internos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" customFormat="1" s="2">
-      <c r="A7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Está documentada en la especificación de la API y en la colección de pruebas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" customFormat="1" s="2">
-      <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Fue revisada por otra persona del equipo antes de integrarse.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="1" s="2">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Se demostró en la revisión de sprint sobre el entorno desplegado, no en local.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="62" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Habilitador</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Por qué se necesita</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Cuándo</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Nota</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Rotar credenciales expuestas en el repositorio</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>cerrar una exposición real de credenciales</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Sprint 1-2</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Crítico. El identificador y el secreto de cliente están escritos en el código de un repositorio público.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="2">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Cerrar los endpoints sin autenticación</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>eliminar la fuga de datos actual</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Sprint 1-2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>El listado de grupos devuelve nombre, correo y rol de todos los usuarios de todas las organizaciones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" customFormat="1" s="2">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Unificar la frontera entre controladores y servicios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>eliminar de raíz la familia de fallos actual</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Sprint 1-2</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Seis endpoints rotos provienen de este único malentendido de diseño, no de seis errores distintos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" customFormat="1" s="2">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Manejo centralizado de errores y respuesta 404</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>que el frontend maneje fallos de forma uniforme</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Sprint 1-2</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" customFormat="1" s="2">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Validar la configuración al arrancar</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>evitar caídas silenciosas en despliegue</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Sprint 1-2</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Es la causa exacta de la caída total en el despliegue de Azure: el error real era ilegible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" customFormat="1" s="2">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Suite de pruebas automatizadas</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>que un refactor no vuelva a romper producción sin aviso</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Sprint 1-2</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>La ausencia de pruebas es la razón directa de que un endpoint que nunca responde llegara a producción.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" customFormat="1" s="2">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Endurecer la configuración de despliegue</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>cumplir lo mínimo esperable en producción</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Continuo</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9" customFormat="1" s="2">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Mantener la documentación de la API al día</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>que quien consuma la API no trabaje a ciegas</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Continuo</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
-  <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="92" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Riesgo</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Impacto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Mitigación</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>El alcance del MVP supera la capacidad real del equipo</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Alto</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Los sprints 9 a 11 concentran la gamificación. Si la velocidad de los primeros tres sprints queda por debajo de 12 puntos, recortar el juego del sprint 11 y entregar el MVP sin él, no correr el resto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="2">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Los tópicos del sprint 6 obligan a migrar datos existentes</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Alto</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Diseñar la estructura de tópicos en el sprint 5, en paralelo a cursos, para que la migración se prepare con una semana de antelación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" customFormat="1" s="2">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>El banco de preguntas llega tarde y arrastra al juego</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Alto</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>El banco está en el sprint 10 y el juego depende de él. Si el banco se retrasa, el juego no entra. Considerar adelantarlo al sprint 8 si hay holgura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" customFormat="1" s="2">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Un juego rejugable convierte el XP en una fuente infinita</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Medio</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>La historia de topes y antiabuso quedó fuera del MVP. Si el juego entra, aplicar al menos la regla de puntaje completo solo en el primer intento como parte de la propia historia del juego.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" customFormat="1" s="2">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Dos repositorios separados desincronizan el contrato de la API</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Medio</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>La especificación de la API es la fuente única. Cualquier cambio de contrato se acuerda antes de implementarse en cualquiera de los dos lados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" customFormat="1" s="2">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Sprints de una semana dejan poco margen ante imprevistos</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Medio</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Reservar el 20 por ciento de la capacidad de cada sprint. No planificar por encima de 15 puntos aunque la velocidad medida lo permita.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="76" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Para qué sirve</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Cuándo</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Prioridad</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Visión de producto</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Qué problema resuelve, para quién y qué lo diferencia. Una página.</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Antes del sprint 1</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Imprescindible</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="2">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Backlog priorizado</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Este documento. Fuente única de qué se construye y en qué orden.</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Vivo, se revisa cada sprint</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Imprescindible</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" customFormat="1" s="2">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Modelo de dominio</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Las entidades, sus relaciones y reglas. Evita que cada quien invente su propio modelo.</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Equipo técnico</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Sprint 1, se actualiza al cambiar el esquema</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Imprescindible</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" customFormat="1" s="2">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Contrato de la API</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Especificación de cada operación. Es lo que permite que dos repositorios avancen en paralelo.</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Equipo técnico</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Vivo, se actualiza con cada historia</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Imprescindible</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" customFormat="1" s="2">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Definición de Hecho</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Cuándo una historia está realmente terminada. Sin esto, cada quien decide por su cuenta.</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Equipo completo</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Antes del sprint 1</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Imprescindible</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" customFormat="1" s="2">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Guía de instalación y ejecución</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Que cualquiera levante el proyecto desde cero sin preguntar.</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Equipo técnico</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Imprescindible</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" customFormat="1" s="2">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Matriz de roles y permisos</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Qué puede hacer cada rol sobre cada recurso. Se prueba contra esta tabla.</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Product Owner y equipo técnico</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Imprescindible</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="1" s="2">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Diseño de la economía de puntos</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Cuánto vale cada acción, cómo se calculan los niveles y qué impide abusar del sistema.</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Antes del sprint 9</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Imprescindible</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" customFormat="1" s="2">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Manual de usuario por rol</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Que un cliente use el producto sin capacitación presencial.</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Sprints 10 y 11</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Recomendable</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" customFormat="1" s="2">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Guía de contribución</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Convenciones de código, ramas y revisiones. Reduce discusiones repetidas.</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Equipo técnico</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Recomendable</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" customFormat="1" s="2">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Registro de decisiones de arquitectura</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Por qué se eligió cada cosa. Evita rediscutir lo ya resuelto y explica el porqué a quien llegue después.</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Equipo técnico</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Vivo</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Recomendable</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" customFormat="1" s="2">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Plan de pruebas y casos de aceptación</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Cómo se verifica cada historia antes de darla por hecha.</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Equipo completo</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Vivo</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Recomendable</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" customFormat="1" s="2">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Runbook de despliegue e incidentes</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Cómo se despliega y qué hacer cuando algo se cae. Se escribe antes de necesitarlo.</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Equipo técnico</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Recomendable</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" customFormat="1" s="2">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Documento de arquitectura</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Vista general de componentes e integraciones externas. Útil para la sustentación académica.</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Equipo técnico</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Recomendable</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" customFormat="1" s="2">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Política de datos personales</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Qué datos se guardan, por cuánto y quién accede. Obligatorio si hay datos de estudiantes reales.</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Antes de datos reales</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Según contexto</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
@@ -8987,557 +8416,303 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Medalla</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Categoría</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Condición para desbloquearla</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de condición</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Cuándo se evalúa</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Nota</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Primer paso</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Progreso</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Completar tu primera actividad</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Actividades completadas</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Al completar una actividad</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>La primera recompensa debe llegar rápido: es la que engancha.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="2">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>En marcha</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Progreso</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Completar 10 actividades</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Actividades completadas</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Al completar una actividad</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" customFormat="1" s="2">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Maratonista</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Progreso</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Completar 50 actividades</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Actividades completadas</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Al completar una actividad</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5" customFormat="1" s="2">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Explorador</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Progreso</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Completar 10 secciones</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Secciones completadas</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Al completar una actividad</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Una sección cuenta como completada cuando todas sus actividades lo están.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" customFormat="1" s="2">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Curso completo</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Progreso</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Terminar tu primer curso al 100%</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Cursos completados</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Al completar una actividad</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>La medalla más importante del catálogo: marca el objetivo real del producto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" customFormat="1" s="2">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Coleccionista</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Progreso</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Terminar 5 cursos completos</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Cursos completados</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Al completar una actividad</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" customFormat="1" s="2">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Constante</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Constancia</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Mantener 7 días seguidos de actividad</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Racha de días activos</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Al completar una actividad</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9" customFormat="1" s="2">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Imparable</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Constancia</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Mantener 30 días seguidos de actividad</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Racha de días activos</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Al completar una actividad</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" customFormat="1" s="2">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Puntual</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Constancia</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Entregar 10 trabajos antes de la fecha límite</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Entregas puntuales</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Al calificarse una entrega</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11" customFormat="1" s="2">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Excelencia</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Desempeño</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Obtener la nota máxima en una evaluación</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Nota mínima obtenida</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Al calificarse una evaluación</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" customFormat="1" s="2">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Impecable</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Desempeño</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Aprobar 5 evaluaciones seguidas sin reprobar ninguna</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Nota mínima obtenida</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Al calificarse una evaluación</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Requiere guardar la racha de aprobados, no solo la última nota.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" customFormat="1" s="2">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Escalador</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Nivel</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Alcanzar el nivel 5</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Nivel alcanzado</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Al acreditarse puntos</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" customFormat="1" s="2">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Cima</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Nivel</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Alcanzar el nivel 10</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Nivel alcanzado</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Al acreditarse puntos</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15" customFormat="1" s="2">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Podio</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Ranking</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Quedar entre los 3 primeros del ranking al cierre de un mes</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Posición en el ranking</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Al cerrar el periodo</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Se evalúa una vez al mes, no en tiempo real. Si se calculara al vuelo, la medalla se otorgaría y quitaría cada pocos minutos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" customFormat="1" s="2">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Número uno</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Ranking</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Quedar primero en el ranking de tu organización al cierre de un mes</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Posición en el ranking</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Al cerrar el periodo</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>El ranking es siempre dentro de la organización, nunca entre clientes distintos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" customFormat="1" s="2">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Juegos</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Completar tu primer juego</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Juegos completados</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Al terminar una partida</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" customFormat="1" s="2">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Maestro del juego</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Juegos</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Completar 10 juegos con puntaje perfecto</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Juegos completados</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Al terminar una partida</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Cuenta la primera vez que se logra el puntaje perfecto en cada juego, no las repeticiones del mismo.</t>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Campo</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Plataforma de onboarding corporativo multiempresa</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Sergio Angel, Brayan Miranda</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Sprints</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>11 · semanales</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Inicio</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>28/8/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Entrega</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>20/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Alcance del MVP</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>226 SP · 64 historias</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Post-MVP en backlog</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>66 SP · 29 historias</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Ultimo corte</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Sprint 6 · 2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr"/>
+      <c r="B10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>KPI del proyecto</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Sprints cerrados</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>6 de 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Avance del MVP</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>103 de 226 SP · 46%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Historias entregadas</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>32 de 34</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Velocidad promedio</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>17.2 SP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Velocidad ultimos 3 sprints</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>19.7 SP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Pronostico cumplido</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>94% · 103 de 109 SP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>SP restantes</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>123 en 5 sprints</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr"/>
+      <c r="B19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>KPI de calidad</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Defectos detectados</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Defectos resueltos</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Defectos mitigados</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Defectos abiertos</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Densidad</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>0.12 por SP entregado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Defectos de seguridad</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>5 de 12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -9548,561 +8723,237 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bloque</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Elemento</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Detalle</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Tipo de condición</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Actividades completadas</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Se configura: cantidad. Ejemplo: 50 actividades.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="2">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Tipo de condición</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Secciones completadas</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Se configura: cantidad. Ejemplo: 10 secciones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" customFormat="1" s="2">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tipo de condición</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Cursos completados</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Se configura: cantidad. Ejemplo: 1 curso al 100%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" customFormat="1" s="2">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Tipo de condición</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Racha de días activos</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Se configura: días seguidos. Ejemplo: 7 días.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" customFormat="1" s="2">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Tipo de condición</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Nivel alcanzado</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Se configura: nivel. Ejemplo: nivel 5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" customFormat="1" s="2">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Tipo de condición</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Nota mínima obtenida</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Se configura: nota y veces. Ejemplo: nota máxima, 1 vez.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" customFormat="1" s="2">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Tipo de condición</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Posición en el ranking</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Se configura: puesto y periodo. Ejemplo: puesto 1 del mes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="1" s="2">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Tipo de condición</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Juegos completados</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Se configura: cantidad y puntaje mínimo. Ejemplo: 10 juegos con puntaje perfecto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" customFormat="1" s="2">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Tipo de condición</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Entregas puntuales</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Se configura: cantidad. Ejemplo: 10 entregas antes del plazo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" customFormat="1" s="2">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Momento de evaluación</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Se completa una actividad</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Medallas de conteo de actividades, secciones y cursos, y de racha de días.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" customFormat="1" s="2">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Momento de evaluación</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Se califica una entrega o evaluación</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Medallas de desempeño (notas) y de entregas a tiempo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" customFormat="1" s="2">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Momento de evaluación</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Se acreditan puntos</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Medallas de nivel alcanzado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" customFormat="1" s="2">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Momento de evaluación</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Termina una partida de un juego</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Medallas de juegos jugados y de puntaje perfecto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" customFormat="1" s="2">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Momento de evaluación</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Cierra un periodo (semana o mes)</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Medallas de posición en el ranking. Es el único disparador programado, no inmediato.</t>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Modulo</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Autenticacion y perfil</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Contrasenas y limite de intentos</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Organizaciones</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Usuarios y roles</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Carga masiva (HU-019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Aislamiento entre organizaciones</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Grupos e integrantes</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Cursos y secciones</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Editar, archivar y publicar (HU-028, HU-029, HU-033)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Actividades y material</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Examenes</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Responder y calificar (HU-044, HU-045), banco de preguntas (HU-043)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Entregas y revision</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>XP, niveles y ranking</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Tabla de niveles configurable (HU-053), antiabuso (HU-055)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Racha de dias activos</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Logros</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Desbloqueo automatico (HU-061), ver mis logros (HU-062)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Juegos</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Sin empezar</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>HU-065, HU-067</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="92" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Escala</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Significado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Story Points</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Trivial. Endpoint ya existe, solo falta UI o un ajuste menor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="2">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Story Points</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>CRUD simple sobre una entidad que ya existe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" customFormat="1" s="2">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Story Points</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>CRUD con validaciones, reglas de rol o filtrado por tenant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" customFormat="1" s="2">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Story Points</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Lógica de negocio nueva, integración externa o cambio de schema.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" customFormat="1" s="2">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Story Points</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Varias entidades nuevas + algoritmo no trivial. Candidata a partirse.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" customFormat="1" s="2">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Story Points</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Es una épica disfrazada. Hay que partirla antes de estimarla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" customFormat="1" s="2">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Valor negocio</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Nice to have.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="1" s="2">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Valor negocio</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Conveniencia. Se puede vivir sin ello un tiempo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" customFormat="1" s="2">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Valor negocio</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Mejora relevante de la experiencia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" customFormat="1" s="2">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Valor negocio</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Diferenciador o núcleo de la propuesta de valor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" customFormat="1" s="2">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Valor negocio</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Sin esto el producto no se puede vender ni usar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" customFormat="1" s="2">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Prioridad</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Sin esto no hay MVP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" customFormat="1" s="2">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Prioridad</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Importante, pero el MVP sobrevive sin ello.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" customFormat="1" s="2">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Prioridad</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Se hace si sobra capacidad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" customFormat="1" s="2">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Prioridad</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Won't</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Explícitamente fuera de este alcance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/tecnico/OnBoardPro-Backlog.xlsx
+++ b/docs/tecnico/OnBoardPro-Backlog.xlsx
@@ -275,12 +275,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Métricas por sprint'!$A$2:$A$7</f>
+              <f>'Métricas por sprint'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Métricas por sprint'!$G$2:$G$7</f>
+              <f>'Métricas por sprint'!$G$2:$G$8</f>
             </numRef>
           </val>
         </ser>
@@ -299,12 +299,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Métricas por sprint'!$A$2:$A$7</f>
+              <f>'Métricas por sprint'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Métricas por sprint'!$H$2:$H$7</f>
+              <f>'Métricas por sprint'!$H$2:$H$8</f>
             </numRef>
           </val>
         </ser>
@@ -419,12 +419,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Métricas por sprint'!$A$2:$A$7</f>
+              <f>'Métricas por sprint'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Métricas por sprint'!$J$2:$J$7</f>
+              <f>'Métricas por sprint'!$J$2:$J$8</f>
             </numRef>
           </val>
         </ser>
@@ -451,12 +451,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Métricas por sprint'!$A$2:$A$7</f>
+              <f>'Métricas por sprint'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Métricas por sprint'!$K$2:$K$7</f>
+              <f>'Métricas por sprint'!$K$2:$K$8</f>
             </numRef>
           </val>
         </ser>
@@ -563,12 +563,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Métricas por sprint'!$A$2:$A$7</f>
+              <f>'Métricas por sprint'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Métricas por sprint'!$L$2:$L$7</f>
+              <f>'Métricas por sprint'!$L$2:$L$8</f>
             </numRef>
           </val>
         </ser>
@@ -7860,23 +7860,33 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="E8" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="F8" s="11" t="n"/>
+      <c r="F8" s="11" t="n">
+        <v>7</v>
+      </c>
       <c r="G8" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="11" t="n"/>
+      <c r="H8" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>130</v>
+      </c>
       <c r="K8" s="11" t="n">
         <v>226</v>
       </c>
-      <c r="L8" s="11" t="n"/>
+      <c r="L8" s="11" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -8032,28 +8042,28 @@
       <c r="C13" s="11" t="inlineStr"/>
       <c r="D13" s="11" t="inlineStr"/>
       <c r="E13" s="11" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>0.945</v>
+        <v>0.9353</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>226</v>
       </c>
       <c r="L13" s="11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -8527,7 +8537,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Sprint 6 · 2026-10-09</t>
+          <t>Sprint 7 · 2026-10-16</t>
         </is>
       </c>
     </row>
@@ -8555,7 +8565,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>6 de 11</t>
+          <t>7 de 11</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8577,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>103 de 226 SP · 46%</t>
+          <t>130 de 226 SP · 58%</t>
         </is>
       </c>
     </row>
@@ -8579,7 +8589,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>32 de 34</t>
+          <t>39 de 42</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8601,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>17.2 SP</t>
+          <t>18.6 SP</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8613,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>19.7 SP</t>
+          <t>23.0 SP</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8625,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>94% · 103 de 109 SP</t>
+          <t>94% · 130 de 139 SP</t>
         </is>
       </c>
     </row>
@@ -8627,7 +8637,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>123 en 5 sprints</t>
+          <t>96 en 4 sprints</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8705,7 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>0.12 por SP entregado</t>
+          <t>0.09 por SP entregado</t>
         </is>
       </c>
     </row>
